--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/1000000/Output_4_13.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/1000000/Output_4_13.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>319229.1376669945</v>
+        <v>324953.9067354489</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2995127.424547407</v>
+        <v>2989156.853416513</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20355556.36745722</v>
+        <v>20349704.61069183</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4813755.887318159</v>
+        <v>4821717.092236059</v>
       </c>
     </row>
     <row r="11">
@@ -892,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -904,10 +904,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -940,7 +940,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>10.61706312961832</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
     </row>
     <row r="6">
@@ -974,16 +974,16 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1083,19 +1083,19 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>19.84491174912431</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1132,19 +1132,19 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>10.95151064538747</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1165,19 +1165,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>12.57565326968602</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1205,25 +1205,25 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>21.81976115797297</v>
       </c>
       <c r="G9" t="n">
-        <v>22.90079999999999</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.27419204266741</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>26</v>
+        <v>23.19571111787229</v>
       </c>
       <c r="J10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="K10" t="n">
         <v>22.26949182588285</v>
@@ -1320,10 +1320,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1360,13 +1360,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1375,10 +1375,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>26</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="I11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1408,16 +1408,16 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -1454,10 +1454,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1484,16 +1484,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1536,13 +1536,13 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>23.19571111787229</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1560,16 +1560,16 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>19.82224313344376</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1600,25 +1600,25 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>10.95151064538747</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>26</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1660,10 +1660,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
     </row>
     <row r="15">
@@ -1685,16 +1685,16 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>22.15420867374215</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>26</v>
+        <v>21.81976115797297</v>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J15" t="n">
         <v>0.7465913262578567</v>
@@ -1724,10 +1724,10 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1773,13 +1773,13 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>23.19571111787227</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1797,16 +1797,16 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>19.82224313344376</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1843,16 +1843,16 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>14.31059503474164</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1876,19 +1876,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>24.66239999999999</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1925,13 +1925,13 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1958,16 +1958,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>24.66239999999999</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>22.44875936050941</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2040,22 +2040,22 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>22.02246762618611</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2068,28 +2068,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1.79691042959408</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2134,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="21">
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -2165,13 +2165,13 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>36.10479393315186</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
-        <v>85.44293011286982</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2226,76 +2226,76 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2305,31 +2305,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2359,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>200.3235106453875</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2374,7 +2374,7 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
     </row>
     <row r="24">
@@ -2384,13 +2384,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
-        <v>140.8900205370621</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -2432,28 +2432,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>91.10663889794492</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="25">
@@ -2472,7 +2472,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2505,13 +2505,13 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>44.30348359856706</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2563,10 +2563,10 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2590,28 +2590,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.265316057196634</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W26" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>80.97850313383185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2621,22 +2621,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D27" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>26.98580820205339</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -2669,10 +2669,10 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>35.21421930193618</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -2684,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>205.7729852034775</v>
@@ -2721,13 +2721,13 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>17.55829564281238</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="C29" t="n">
-        <v>241</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -2791,10 +2791,10 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>29.85921600351671</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2827,7 +2827,7 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -2839,13 +2839,13 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>202.2821007854552</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -2864,10 +2864,10 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2912,22 +2912,22 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>189.7190331592112</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="W30" t="n">
-        <v>241</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X30" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>182.6630774502249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2937,76 +2937,76 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3019,19 +3019,19 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="D32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3067,13 +3067,13 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>189.372</v>
+        <v>189.7190331592112</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>112.3716363300954</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D33" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E33" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>66.80154844887949</v>
       </c>
     </row>
     <row r="34">
@@ -3195,13 +3195,13 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>17.55829564281238</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -3234,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>179.7283339446664</v>
       </c>
       <c r="C35" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="D35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3307,22 +3307,22 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="U35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>189.372</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3332,22 +3332,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>66.29785012506153</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D36" t="n">
-        <v>147.4450655646388</v>
+        <v>141.8677101808313</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -3380,10 +3380,10 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
@@ -3395,10 +3395,10 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3490,25 +3490,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>189.7190331592112</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3535,13 +3535,13 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>179.3813007854552</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -3550,7 +3550,7 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -3572,10 +3572,10 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>5.255165712911821</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D39" t="n">
-        <v>147.4450655646388</v>
+        <v>118.4702779777132</v>
       </c>
       <c r="E39" t="n">
         <v>157.6450804554009</v>
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -3632,7 +3632,7 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -3736,22 +3736,22 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>166.0441028249983</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3793,10 +3793,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="Y41" t="n">
-        <v>177.6197007854552</v>
+        <v>213.4242636173429</v>
       </c>
     </row>
     <row r="42">
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3860,16 +3860,16 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>195.635369808021</v>
       </c>
       <c r="V42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="W42" t="n">
-        <v>117.5294619240279</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="X42" t="n">
         <v>205.7729852034775</v>
@@ -3933,22 +3933,22 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -4526,76 +4526,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>65.87777657221105</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>65.87777657221105</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>65.87777657221105</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>39.99869455743244</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>39.99869455743244</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>39.99869455743244</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>39.99869455743244</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>91.75685858698967</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>91.75685858698967</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>91.75685858698967</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>91.75685858698967</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>65.87777657221105</v>
       </c>
     </row>
     <row r="6">
@@ -4605,76 +4605,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="7">
@@ -4684,76 +4684,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>47.97407071350496</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="8">
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C8" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D8" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E8" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F8" t="n">
-        <v>92.93786803496215</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G8" t="n">
-        <v>66.67524177233588</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H8" t="n">
-        <v>40.41261550970962</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I8" t="n">
-        <v>14.14998924708335</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J8" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K8" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L8" t="n">
-        <v>2.08</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M8" t="n">
-        <v>27.82</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N8" t="n">
-        <v>53.56</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O8" t="n">
-        <v>78.26000000000001</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q8" t="n">
-        <v>104</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="R8" t="n">
-        <v>104</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="S8" t="n">
-        <v>104</v>
+        <v>40.631385380739</v>
       </c>
       <c r="T8" t="n">
-        <v>104</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="U8" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V8" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W8" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X8" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y8" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D9" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E9" t="n">
-        <v>51.47474747474747</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F9" t="n">
-        <v>25.2121212121212</v>
+        <v>80.44100199269204</v>
       </c>
       <c r="G9" t="n">
-        <v>2.08</v>
+        <v>54.56191997791342</v>
       </c>
       <c r="H9" t="n">
-        <v>2.08</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="I9" t="n">
-        <v>2.08</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="J9" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K9" t="n">
-        <v>27.82</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L9" t="n">
-        <v>53.56</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="M9" t="n">
-        <v>79.3</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="N9" t="n">
-        <v>104</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="O9" t="n">
-        <v>104</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="P9" t="n">
-        <v>104</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="C10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="D10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="E10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="F10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="G10" t="n">
-        <v>103.3623149756393</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="H10" t="n">
-        <v>77.09968871301299</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="I10" t="n">
-        <v>50.83706245038672</v>
+        <v>50.42314149810954</v>
       </c>
       <c r="J10" t="n">
-        <v>24.57443618776046</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="K10" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L10" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M10" t="n">
-        <v>53.56</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N10" t="n">
-        <v>79.3</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O10" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P10" t="n">
-        <v>103.6392766348993</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="Q10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="R10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="S10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="T10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="U10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="V10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="W10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="X10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="Y10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>54.60525252525252</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="C11" t="n">
-        <v>54.60525252525252</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="D11" t="n">
-        <v>54.60525252525252</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="E11" t="n">
-        <v>54.60525252525252</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="F11" t="n">
-        <v>54.60525252525252</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="G11" t="n">
-        <v>54.60525252525252</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="H11" t="n">
-        <v>28.34262626262626</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K11" t="n">
-        <v>27.82</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L11" t="n">
-        <v>53.56</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M11" t="n">
-        <v>78.26000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="N11" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O11" t="n">
-        <v>78.26000000000001</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S11" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="T11" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="U11" t="n">
-        <v>77.73737373737373</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="V11" t="n">
-        <v>54.60525252525252</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="W11" t="n">
-        <v>54.60525252525252</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="X11" t="n">
-        <v>54.60525252525252</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="Y11" t="n">
-        <v>54.60525252525252</v>
+        <v>76.6020827637447</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51.47474747474747</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C12" t="n">
-        <v>51.47474747474747</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D12" t="n">
-        <v>51.47474747474747</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E12" t="n">
-        <v>51.47474747474747</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F12" t="n">
-        <v>51.47474747474747</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G12" t="n">
-        <v>51.47474747474747</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H12" t="n">
-        <v>28.34262626262626</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I12" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J12" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K12" t="n">
-        <v>27.82</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L12" t="n">
-        <v>53.56</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="M12" t="n">
-        <v>79.3</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="N12" t="n">
-        <v>104</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O12" t="n">
-        <v>104</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R12" t="n">
-        <v>77.73737373737373</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S12" t="n">
-        <v>51.47474747474747</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="T12" t="n">
-        <v>51.47474747474747</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="U12" t="n">
-        <v>51.47474747474747</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V12" t="n">
-        <v>51.47474747474747</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W12" t="n">
-        <v>51.47474747474747</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X12" t="n">
-        <v>51.47474747474747</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y12" t="n">
-        <v>51.47474747474747</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="C13" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="D13" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="E13" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="F13" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="G13" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="H13" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="I13" t="n">
-        <v>2.44072336510073</v>
+        <v>50.42314149810954</v>
       </c>
       <c r="J13" t="n">
-        <v>2.44072336510073</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="K13" t="n">
-        <v>2.44072336510073</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L13" t="n">
-        <v>28.18072336510073</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M13" t="n">
-        <v>53.92072336510073</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N13" t="n">
-        <v>79.66072336510072</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O13" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P13" t="n">
-        <v>101.2510699645389</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="Q13" t="n">
-        <v>74.98844370191262</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="R13" t="n">
-        <v>48.72581743928635</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="S13" t="n">
-        <v>22.46319117666009</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="T13" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="U13" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="V13" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="W13" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="X13" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828358</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="C14" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="D14" t="n">
-        <v>92.93786803496215</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="E14" t="n">
-        <v>66.67524177233588</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="F14" t="n">
-        <v>66.67524177233588</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G14" t="n">
-        <v>40.41261550970962</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H14" t="n">
-        <v>14.14998924708335</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I14" t="n">
-        <v>14.14998924708335</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K14" t="n">
-        <v>27.82</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L14" t="n">
-        <v>53.56</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M14" t="n">
-        <v>53.56</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N14" t="n">
-        <v>53.56</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O14" t="n">
-        <v>78.26000000000001</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X14" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="Y14" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="C15" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="D15" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="E15" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="F15" t="n">
-        <v>81.62201144066449</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="G15" t="n">
-        <v>55.35938517803824</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="H15" t="n">
-        <v>29.09675891541198</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="I15" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="J15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L15" t="n">
-        <v>26.78000000000001</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="M15" t="n">
-        <v>52.52000000000001</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="N15" t="n">
-        <v>78.26000000000001</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="O15" t="n">
-        <v>78.26000000000001</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="P15" t="n">
-        <v>78.26000000000001</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S15" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="T15" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="U15" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="V15" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="W15" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="X15" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="Y15" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828356</v>
       </c>
       <c r="C16" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828356</v>
       </c>
       <c r="D16" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828356</v>
       </c>
       <c r="E16" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828356</v>
       </c>
       <c r="F16" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828356</v>
       </c>
       <c r="G16" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828356</v>
       </c>
       <c r="H16" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828356</v>
       </c>
       <c r="I16" t="n">
-        <v>2.44072336510073</v>
+        <v>50.42314149810954</v>
       </c>
       <c r="J16" t="n">
-        <v>2.44072336510073</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="K16" t="n">
-        <v>2.44072336510073</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L16" t="n">
-        <v>28.18072336510073</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M16" t="n">
-        <v>53.92072336510073</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N16" t="n">
-        <v>79.66072336510072</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P16" t="n">
-        <v>101.2510699645389</v>
+        <v>99.73223474306218</v>
       </c>
       <c r="Q16" t="n">
-        <v>74.98844370191262</v>
+        <v>73.85315272828356</v>
       </c>
       <c r="R16" t="n">
-        <v>48.72581743928635</v>
+        <v>73.85315272828356</v>
       </c>
       <c r="S16" t="n">
-        <v>22.46319117666009</v>
+        <v>73.85315272828356</v>
       </c>
       <c r="T16" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828356</v>
       </c>
       <c r="U16" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828356</v>
       </c>
       <c r="V16" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828356</v>
       </c>
       <c r="W16" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828356</v>
       </c>
       <c r="X16" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828356</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.44072336510073</v>
+        <v>73.85315272828356</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.24</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="C17" t="n">
-        <v>2.24</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="D17" t="n">
-        <v>2.24</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="E17" t="n">
-        <v>2.24</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="F17" t="n">
-        <v>2.24</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="H17" t="n">
-        <v>2.24</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="I17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K17" t="n">
-        <v>2.24</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L17" t="n">
-        <v>29.96</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="M17" t="n">
-        <v>57.68</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="N17" t="n">
-        <v>84.28</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="O17" t="n">
-        <v>84.28</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q17" t="n">
-        <v>112</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="R17" t="n">
-        <v>83.71717171717171</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="S17" t="n">
-        <v>55.43434343434343</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="T17" t="n">
-        <v>27.15151515151514</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="U17" t="n">
-        <v>2.24</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="V17" t="n">
-        <v>2.24</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="W17" t="n">
-        <v>2.24</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="X17" t="n">
-        <v>2.24</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.24</v>
+        <v>100.2684856730375</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.24</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="C18" t="n">
-        <v>2.24</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="D18" t="n">
-        <v>2.24</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="E18" t="n">
-        <v>2.24</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="F18" t="n">
-        <v>2.24</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="G18" t="n">
-        <v>2.24</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="H18" t="n">
-        <v>2.24</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="I18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L18" t="n">
-        <v>2.24</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M18" t="n">
-        <v>2.24</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="N18" t="n">
-        <v>28.84</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="O18" t="n">
-        <v>56.56</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P18" t="n">
-        <v>84.28</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R18" t="n">
-        <v>83.71717171717171</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="S18" t="n">
-        <v>55.43434343434343</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="T18" t="n">
-        <v>27.15151515151514</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="U18" t="n">
-        <v>2.24</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="V18" t="n">
-        <v>2.24</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="W18" t="n">
-        <v>2.24</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="X18" t="n">
-        <v>2.24</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.24</v>
+        <v>82.49138865710684</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.24</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="C19" t="n">
-        <v>2.24</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="D19" t="n">
-        <v>2.24</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="E19" t="n">
-        <v>2.24</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L19" t="n">
-        <v>29.55412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M19" t="n">
-        <v>57.27412500771297</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N19" t="n">
-        <v>84.99412500771297</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="R19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="S19" t="n">
-        <v>109.3334016426122</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="T19" t="n">
-        <v>81.05057335978395</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="U19" t="n">
-        <v>52.76774507695567</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="V19" t="n">
-        <v>52.76774507695567</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="W19" t="n">
-        <v>24.48491679412739</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="X19" t="n">
-        <v>2.24</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.24</v>
+        <v>80.62014129470579</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>964</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C20" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D20" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E20" t="n">
-        <v>962.184938960006</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F20" t="n">
-        <v>718.7505955256626</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G20" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H20" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R20" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S20" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T20" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U20" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V20" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W20" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="X20" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="Y20" t="n">
-        <v>964</v>
+        <v>506.1786963984129</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.28</v>
+        <v>146.8043937272075</v>
       </c>
       <c r="C21" t="n">
-        <v>19.28</v>
+        <v>146.8043937272075</v>
       </c>
       <c r="D21" t="n">
-        <v>19.28</v>
+        <v>146.8043937272075</v>
       </c>
       <c r="E21" t="n">
-        <v>19.28</v>
+        <v>146.8043937272075</v>
       </c>
       <c r="F21" t="n">
-        <v>19.28</v>
+        <v>146.8043937272075</v>
       </c>
       <c r="G21" t="n">
-        <v>19.28</v>
+        <v>146.8043937272075</v>
       </c>
       <c r="H21" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I21" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L21" t="n">
-        <v>304.1765223866491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M21" t="n">
-        <v>304.1765223866491</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N21" t="n">
-        <v>542.7665223866492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O21" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>689.4131260035546</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T21" t="n">
-        <v>603.1071359905548</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="U21" t="n">
-        <v>603.1071359905548</v>
+        <v>562.4161926976942</v>
       </c>
       <c r="V21" t="n">
-        <v>603.1071359905548</v>
+        <v>562.4161926976942</v>
       </c>
       <c r="W21" t="n">
-        <v>603.1071359905548</v>
+        <v>562.4161926976942</v>
       </c>
       <c r="X21" t="n">
-        <v>395.2556357850219</v>
+        <v>354.5646924921614</v>
       </c>
       <c r="Y21" t="n">
-        <v>187.495337020068</v>
+        <v>146.8043937272075</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>761.6530195501136</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C23" t="n">
-        <v>761.6530195501136</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D23" t="n">
-        <v>761.6530195501136</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E23" t="n">
-        <v>761.6530195501136</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F23" t="n">
-        <v>518.2186761157702</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G23" t="n">
-        <v>274.7843326814268</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H23" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I23" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R23" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S23" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T23" t="n">
-        <v>761.6530195501136</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U23" t="n">
-        <v>761.6530195501136</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V23" t="n">
-        <v>761.6530195501136</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W23" t="n">
-        <v>761.6530195501136</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="X23" t="n">
-        <v>761.6530195501136</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="Y23" t="n">
-        <v>761.6530195501136</v>
+        <v>749.627473042513</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>310.5275617188897</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C24" t="n">
-        <v>168.2144096612513</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L24" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M24" t="n">
-        <v>249.2431058683491</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N24" t="n">
-        <v>473.3719638733197</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O24" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P24" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S24" t="n">
-        <v>964</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T24" t="n">
-        <v>761.813405358766</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U24" t="n">
-        <v>761.813405358766</v>
+        <v>395.2567788952347</v>
       </c>
       <c r="V24" t="n">
-        <v>761.813405358766</v>
+        <v>395.2567788952347</v>
       </c>
       <c r="W24" t="n">
-        <v>518.3790619244226</v>
+        <v>395.2567788952347</v>
       </c>
       <c r="X24" t="n">
-        <v>310.5275617188897</v>
+        <v>395.2567788952347</v>
       </c>
       <c r="Y24" t="n">
-        <v>310.5275617188897</v>
+        <v>187.4964801302808</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C25" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D25" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>961.308225475175</v>
       </c>
       <c r="Q25" t="n">
-        <v>153.8122904902707</v>
+        <v>874.2758585542716</v>
       </c>
       <c r="R25" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="S25" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="T25" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="U25" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="V25" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="W25" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="X25" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="Y25" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C26" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D26" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E26" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F26" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G26" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H26" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I26" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R26" t="n">
-        <v>812.6170525846973</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S26" t="n">
-        <v>812.6170525846973</v>
+        <v>752.9257720901863</v>
       </c>
       <c r="T26" t="n">
-        <v>812.6170525846973</v>
+        <v>749.627473042513</v>
       </c>
       <c r="U26" t="n">
-        <v>812.6170525846973</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="V26" t="n">
-        <v>812.6170525846973</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="W26" t="n">
-        <v>569.1827091503538</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X26" t="n">
-        <v>325.7483657160104</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y26" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>168.2144096612513</v>
+        <v>380.2300195200815</v>
       </c>
       <c r="C27" t="n">
-        <v>168.2144096612513</v>
+        <v>205.7769902389545</v>
       </c>
       <c r="D27" t="n">
-        <v>19.28</v>
+        <v>205.7769902389545</v>
       </c>
       <c r="E27" t="n">
-        <v>19.28</v>
+        <v>46.53953523349898</v>
       </c>
       <c r="F27" t="n">
-        <v>19.28</v>
+        <v>46.53953523349898</v>
       </c>
       <c r="G27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L27" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M27" t="n">
-        <v>374.6006659261865</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="N27" t="n">
-        <v>473.3719638733197</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O27" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P27" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S27" t="n">
-        <v>827.2605520660815</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T27" t="n">
-        <v>827.2605520660815</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U27" t="n">
-        <v>827.2605520660815</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V27" t="n">
-        <v>827.2605520660815</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W27" t="n">
-        <v>583.826208631738</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X27" t="n">
-        <v>375.9747084262052</v>
+        <v>756.2056553051034</v>
       </c>
       <c r="Y27" t="n">
-        <v>168.2144096612513</v>
+        <v>548.4453565401495</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>262.7143434343434</v>
+        <v>482.5317333192617</v>
       </c>
       <c r="C29" t="n">
-        <v>19.28</v>
+        <v>264.9620386899402</v>
       </c>
       <c r="D29" t="n">
-        <v>19.28</v>
+        <v>264.9620386899402</v>
       </c>
       <c r="E29" t="n">
-        <v>19.28</v>
+        <v>264.9620386899402</v>
       </c>
       <c r="F29" t="n">
-        <v>19.28</v>
+        <v>47.39234406061874</v>
       </c>
       <c r="G29" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2389935104989</v>
+        <v>23.55055379931807</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3148450951575</v>
+        <v>203.6264053839766</v>
       </c>
       <c r="M29" t="n">
-        <v>519.2904723580616</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N29" t="n">
-        <v>725.144994565301</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O29" t="n">
-        <v>874.339944707949</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P29" t="n">
-        <v>964</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q29" t="n">
-        <v>953.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="R29" t="n">
-        <v>953.9083846317729</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="S29" t="n">
-        <v>953.9083846317729</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="T29" t="n">
-        <v>953.9083846317729</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="U29" t="n">
-        <v>953.9083846317729</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="V29" t="n">
-        <v>710.4740411974295</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="W29" t="n">
-        <v>467.0396977630861</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="X29" t="n">
-        <v>262.7143434343434</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="Y29" t="n">
-        <v>262.7143434343434</v>
+        <v>700.1014279485831</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>328.2059973194925</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C30" t="n">
-        <v>328.2059973194925</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D30" t="n">
-        <v>179.2715876582412</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E30" t="n">
-        <v>20.03413265278571</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F30" t="n">
-        <v>20.03413265278571</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G30" t="n">
-        <v>20.03413265278571</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H30" t="n">
-        <v>20.03413265278571</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I30" t="n">
-        <v>20.03413265278571</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K30" t="n">
-        <v>19.28</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L30" t="n">
-        <v>249.2431058683491</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="M30" t="n">
-        <v>473.3719638733197</v>
+        <v>183.0578391930369</v>
       </c>
       <c r="N30" t="n">
-        <v>473.3719638733197</v>
+        <v>396.2978968992348</v>
       </c>
       <c r="O30" t="n">
-        <v>711.9619638733197</v>
+        <v>609.5379546054328</v>
       </c>
       <c r="P30" t="n">
-        <v>894.6054414866707</v>
+        <v>792.1814322187836</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S30" t="n">
-        <v>964</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T30" t="n">
-        <v>964</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="U30" t="n">
-        <v>964</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="V30" t="n">
-        <v>964</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="W30" t="n">
-        <v>720.5656565656566</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="X30" t="n">
-        <v>512.7141563601238</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y30" t="n">
-        <v>328.2059973194925</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>829.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C31" t="n">
-        <v>829.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D31" t="n">
-        <v>829.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E31" t="n">
-        <v>829.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F31" t="n">
-        <v>829.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G31" t="n">
-        <v>829.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H31" t="n">
-        <v>829.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I31" t="n">
-        <v>829.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J31" t="n">
-        <v>829.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K31" t="n">
-        <v>829.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L31" t="n">
-        <v>856.7818345174422</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M31" t="n">
-        <v>895.9698727096644</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N31" t="n">
-        <v>939.6607233651007</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O31" t="n">
-        <v>964</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P31" t="n">
-        <v>964</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q31" t="n">
-        <v>964</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R31" t="n">
-        <v>964</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S31" t="n">
-        <v>964</v>
+        <v>151.763810304913</v>
       </c>
       <c r="T31" t="n">
-        <v>964</v>
+        <v>151.763810304913</v>
       </c>
       <c r="U31" t="n">
-        <v>964</v>
+        <v>151.763810304913</v>
       </c>
       <c r="V31" t="n">
-        <v>964</v>
+        <v>151.763810304913</v>
       </c>
       <c r="W31" t="n">
-        <v>964</v>
+        <v>151.763810304913</v>
       </c>
       <c r="X31" t="n">
-        <v>964</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Y31" t="n">
-        <v>964</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>668.7151515151515</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="C32" t="n">
-        <v>668.7151515151515</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D32" t="n">
-        <v>451.5434343434343</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E32" t="n">
-        <v>451.5434343434343</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F32" t="n">
-        <v>234.3717171717172</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K32" t="n">
-        <v>112.0246760654541</v>
+        <v>23.55055379931807</v>
       </c>
       <c r="L32" t="n">
-        <v>292.1005276501127</v>
+        <v>203.6264053839766</v>
       </c>
       <c r="M32" t="n">
-        <v>504.9505276501126</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N32" t="n">
-        <v>710.8050498573519</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O32" t="n">
-        <v>860</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P32" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q32" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R32" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S32" t="n">
-        <v>668.7151515151515</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="T32" t="n">
-        <v>668.7151515151515</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="U32" t="n">
-        <v>668.7151515151515</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="V32" t="n">
-        <v>668.7151515151515</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="W32" t="n">
-        <v>668.7151515151515</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="X32" t="n">
-        <v>668.7151515151515</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="Y32" t="n">
-        <v>668.7151515151515</v>
+        <v>234.8012144439637</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>471.9064226398218</v>
+        <v>625.8843421475201</v>
       </c>
       <c r="C33" t="n">
-        <v>471.9064226398218</v>
+        <v>451.4313128663931</v>
       </c>
       <c r="D33" t="n">
-        <v>322.9720129785705</v>
+        <v>302.4969032051418</v>
       </c>
       <c r="E33" t="n">
-        <v>163.734557973115</v>
+        <v>302.4969032051418</v>
       </c>
       <c r="F33" t="n">
-        <v>17.2</v>
+        <v>155.9623452320268</v>
       </c>
       <c r="G33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K33" t="n">
-        <v>142.5575600578374</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L33" t="n">
-        <v>355.4075600578374</v>
+        <v>355.8291375786776</v>
       </c>
       <c r="M33" t="n">
-        <v>568.2575600578374</v>
+        <v>569.0691952848756</v>
       </c>
       <c r="N33" t="n">
-        <v>781.1075600578374</v>
+        <v>569.0691952848756</v>
       </c>
       <c r="O33" t="n">
-        <v>860</v>
+        <v>609.5379546054328</v>
       </c>
       <c r="P33" t="n">
-        <v>860</v>
+        <v>792.1814322187836</v>
       </c>
       <c r="Q33" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R33" t="n">
-        <v>758.8304705528857</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S33" t="n">
-        <v>585.4131260035546</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T33" t="n">
-        <v>585.4131260035546</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U33" t="n">
-        <v>585.4131260035546</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="V33" t="n">
-        <v>585.4131260035546</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="W33" t="n">
-        <v>585.4131260035546</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="X33" t="n">
-        <v>585.4131260035546</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Y33" t="n">
-        <v>585.4131260035546</v>
+        <v>794.0996791675882</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.2</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="C34" t="n">
-        <v>17.2</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="D34" t="n">
-        <v>17.2</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="E34" t="n">
-        <v>17.2</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="F34" t="n">
-        <v>17.2</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="G34" t="n">
-        <v>17.2</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="H34" t="n">
-        <v>17.2</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="I34" t="n">
-        <v>17.2</v>
+        <v>843.840338567656</v>
       </c>
       <c r="J34" t="n">
-        <v>17.2</v>
+        <v>749.5381364296027</v>
       </c>
       <c r="K34" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="L34" t="n">
-        <v>44.51412500771298</v>
+        <v>754.3578252495552</v>
       </c>
       <c r="M34" t="n">
-        <v>83.70216319993516</v>
+        <v>793.5458634417773</v>
       </c>
       <c r="N34" t="n">
-        <v>127.3930138553715</v>
+        <v>837.2367140972136</v>
       </c>
       <c r="O34" t="n">
-        <v>151.7322904902707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="P34" t="n">
-        <v>151.7322904902707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q34" t="n">
-        <v>151.7322904902707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R34" t="n">
-        <v>151.7322904902707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S34" t="n">
-        <v>151.7322904902707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T34" t="n">
-        <v>151.7322904902707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U34" t="n">
-        <v>151.7322904902707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="V34" t="n">
-        <v>17.2</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="W34" t="n">
-        <v>17.2</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="X34" t="n">
-        <v>17.2</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Y34" t="n">
-        <v>17.2</v>
+        <v>861.5759907321129</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>451.5434343434343</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="C35" t="n">
-        <v>234.3717171717172</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K35" t="n">
-        <v>120.2150059109224</v>
+        <v>120.2465257255646</v>
       </c>
       <c r="L35" t="n">
-        <v>300.290857495581</v>
+        <v>300.3223773102232</v>
       </c>
       <c r="M35" t="n">
-        <v>513.1408574955809</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N35" t="n">
-        <v>718.9953797028202</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O35" t="n">
-        <v>860</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P35" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q35" t="n">
-        <v>860</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="R35" t="n">
-        <v>860</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="S35" t="n">
-        <v>860</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="T35" t="n">
-        <v>860</v>
+        <v>633.9146807345644</v>
       </c>
       <c r="U35" t="n">
-        <v>642.8282828282828</v>
+        <v>633.9146807345644</v>
       </c>
       <c r="V35" t="n">
-        <v>642.8282828282828</v>
+        <v>633.9146807345644</v>
       </c>
       <c r="W35" t="n">
-        <v>642.8282828282828</v>
+        <v>416.3449861052429</v>
       </c>
       <c r="X35" t="n">
-        <v>642.8282828282828</v>
+        <v>416.3449861052429</v>
       </c>
       <c r="Y35" t="n">
-        <v>451.5434343434343</v>
+        <v>416.3449861052429</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>518.3673184306008</v>
+        <v>334.9852664501443</v>
       </c>
       <c r="C36" t="n">
-        <v>451.3997930517507</v>
+        <v>160.5322371690173</v>
       </c>
       <c r="D36" t="n">
-        <v>302.4653833904995</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E36" t="n">
-        <v>302.4653833904995</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F36" t="n">
-        <v>155.9308254173845</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L36" t="n">
-        <v>230.05</v>
+        <v>230.4715775208402</v>
       </c>
       <c r="M36" t="n">
-        <v>442.9</v>
+        <v>435.095875319717</v>
       </c>
       <c r="N36" t="n">
-        <v>647.15</v>
+        <v>648.335933025915</v>
       </c>
       <c r="O36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="P36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R36" t="n">
-        <v>860</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="S36" t="n">
-        <v>686.5826554506689</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="T36" t="n">
-        <v>686.5826554506689</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="U36" t="n">
-        <v>686.5826554506689</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="V36" t="n">
-        <v>686.5826554506689</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="W36" t="n">
-        <v>686.5826554506689</v>
+        <v>542.8367666556771</v>
       </c>
       <c r="X36" t="n">
-        <v>686.5826554506689</v>
+        <v>334.9852664501443</v>
       </c>
       <c r="Y36" t="n">
-        <v>686.5826554506689</v>
+        <v>334.9852664501443</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="C37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L37" t="n">
-        <v>44.51412500771298</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M37" t="n">
-        <v>83.70216319993516</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N37" t="n">
-        <v>127.3930138553715</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="T37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="U37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="V37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="W37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="X37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Y37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>451.5434343434343</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="C38" t="n">
-        <v>451.5434343434343</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="D38" t="n">
-        <v>451.5434343434343</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="E38" t="n">
-        <v>451.5434343434343</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="F38" t="n">
-        <v>234.3717171717172</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="G38" t="n">
-        <v>17.2</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="H38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K38" t="n">
-        <v>120.2150059109224</v>
+        <v>120.2465257255646</v>
       </c>
       <c r="L38" t="n">
-        <v>300.290857495581</v>
+        <v>300.3223773102232</v>
       </c>
       <c r="M38" t="n">
-        <v>513.1408574955809</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N38" t="n">
-        <v>718.9953797028202</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O38" t="n">
-        <v>860</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q38" t="n">
-        <v>849.9083846317729</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R38" t="n">
-        <v>849.9083846317729</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S38" t="n">
-        <v>668.7151515151515</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T38" t="n">
-        <v>668.7151515151515</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U38" t="n">
-        <v>668.7151515151515</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="V38" t="n">
-        <v>451.5434343434343</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="W38" t="n">
-        <v>451.5434343434343</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="X38" t="n">
-        <v>451.5434343434343</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Y38" t="n">
-        <v>451.5434343434343</v>
+        <v>861.5759907321129</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>469.4109382789517</v>
+        <v>470.5889515534603</v>
       </c>
       <c r="C39" t="n">
-        <v>464.1026900840913</v>
+        <v>296.1359222723333</v>
       </c>
       <c r="D39" t="n">
-        <v>315.16828042284</v>
+        <v>176.4689748200978</v>
       </c>
       <c r="E39" t="n">
-        <v>155.9308254173845</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F39" t="n">
-        <v>155.9308254173845</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K39" t="n">
-        <v>17.2</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L39" t="n">
-        <v>230.05</v>
+        <v>355.8291375786776</v>
       </c>
       <c r="M39" t="n">
-        <v>442.9</v>
+        <v>569.0691952848756</v>
       </c>
       <c r="N39" t="n">
-        <v>655.75</v>
+        <v>609.5379546054328</v>
       </c>
       <c r="O39" t="n">
-        <v>790.6054414866707</v>
+        <v>609.5379546054328</v>
       </c>
       <c r="P39" t="n">
-        <v>790.6054414866707</v>
+        <v>792.1814322187836</v>
       </c>
       <c r="Q39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S39" t="n">
-        <v>686.5826554506689</v>
+        <v>688.1586461827818</v>
       </c>
       <c r="T39" t="n">
-        <v>686.5826554506689</v>
+        <v>688.1586461827818</v>
       </c>
       <c r="U39" t="n">
-        <v>686.5826554506689</v>
+        <v>688.1586461827818</v>
       </c>
       <c r="V39" t="n">
-        <v>686.5826554506689</v>
+        <v>688.1586461827818</v>
       </c>
       <c r="W39" t="n">
-        <v>469.4109382789517</v>
+        <v>470.5889515534603</v>
       </c>
       <c r="X39" t="n">
-        <v>469.4109382789517</v>
+        <v>470.5889515534603</v>
       </c>
       <c r="Y39" t="n">
-        <v>469.4109382789517</v>
+        <v>470.5889515534603</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L40" t="n">
-        <v>44.51412500771298</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M40" t="n">
-        <v>83.70216319993516</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N40" t="n">
-        <v>127.3930138553715</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O40" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P40" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q40" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R40" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S40" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="T40" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="U40" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="V40" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="W40" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="X40" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y40" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>232.1915151515151</v>
+        <v>412.4453105812599</v>
       </c>
       <c r="C41" t="n">
-        <v>232.1915151515151</v>
+        <v>412.4453105812599</v>
       </c>
       <c r="D41" t="n">
-        <v>232.1915151515151</v>
+        <v>412.4453105812599</v>
       </c>
       <c r="E41" t="n">
-        <v>17.04</v>
+        <v>412.4453105812599</v>
       </c>
       <c r="F41" t="n">
-        <v>17.04</v>
+        <v>412.4453105812599</v>
       </c>
       <c r="G41" t="n">
-        <v>17.04</v>
+        <v>196.8652463213176</v>
       </c>
       <c r="H41" t="n">
-        <v>17.04</v>
+        <v>196.8652463213176</v>
       </c>
       <c r="I41" t="n">
-        <v>17.04</v>
+        <v>29.14393033647078</v>
       </c>
       <c r="J41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K41" t="n">
-        <v>17.04</v>
+        <v>120.0889470003098</v>
       </c>
       <c r="L41" t="n">
-        <v>197.1158515846586</v>
+        <v>197.6975058462639</v>
       </c>
       <c r="M41" t="n">
-        <v>407.2904723580617</v>
+        <v>408.9875268274333</v>
       </c>
       <c r="N41" t="n">
-        <v>613.144994565301</v>
+        <v>614.8420490346726</v>
       </c>
       <c r="O41" t="n">
-        <v>762.339944707949</v>
+        <v>764.0369991773207</v>
       </c>
       <c r="P41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q41" t="n">
-        <v>841.9083846317729</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="R41" t="n">
-        <v>841.9083846317729</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="S41" t="n">
-        <v>841.9083846317729</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="T41" t="n">
-        <v>841.9083846317729</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="U41" t="n">
-        <v>841.9083846317729</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="V41" t="n">
-        <v>841.9083846317729</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="W41" t="n">
-        <v>841.9083846317729</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="X41" t="n">
-        <v>626.7568694802578</v>
+        <v>628.0253748412023</v>
       </c>
       <c r="Y41" t="n">
-        <v>447.3430303030303</v>
+        <v>412.4453105812599</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>108.0937617956292</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="C42" t="n">
-        <v>108.0937617956292</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="D42" t="n">
-        <v>108.0937617956292</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="E42" t="n">
-        <v>108.0937617956292</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F42" t="n">
-        <v>108.0937617956292</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G42" t="n">
-        <v>108.0937617956292</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H42" t="n">
-        <v>108.0937617956292</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I42" t="n">
-        <v>17.79413265278571</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K42" t="n">
-        <v>142.3975600578374</v>
+        <v>142.4315011472248</v>
       </c>
       <c r="L42" t="n">
-        <v>353.2675600578374</v>
+        <v>353.7215221283943</v>
       </c>
       <c r="M42" t="n">
-        <v>458.4865223866492</v>
+        <v>565.0115431095638</v>
       </c>
       <c r="N42" t="n">
-        <v>669.3565223866492</v>
+        <v>601.6590183426915</v>
       </c>
       <c r="O42" t="n">
-        <v>669.3565223866492</v>
+        <v>601.6590183426915</v>
       </c>
       <c r="P42" t="n">
-        <v>852</v>
+        <v>784.3024959560423</v>
       </c>
       <c r="Q42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T42" t="n">
-        <v>649.813405358766</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="U42" t="n">
-        <v>649.813405358766</v>
+        <v>656.085569814805</v>
       </c>
       <c r="V42" t="n">
-        <v>434.6618902072508</v>
+        <v>440.5055055548626</v>
       </c>
       <c r="W42" t="n">
-        <v>315.9452620011621</v>
+        <v>224.9254412949203</v>
       </c>
       <c r="X42" t="n">
-        <v>108.0937617956292</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="Y42" t="n">
-        <v>108.0937617956292</v>
+        <v>17.07394108938743</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="C43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="D43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="E43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L43" t="n">
-        <v>44.35412500771298</v>
+        <v>44.38806609710041</v>
       </c>
       <c r="M43" t="n">
-        <v>83.54216319993516</v>
+        <v>83.57610428932259</v>
       </c>
       <c r="N43" t="n">
-        <v>127.2330138553715</v>
+        <v>127.2669549447589</v>
       </c>
       <c r="O43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="P43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="Q43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="R43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="S43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="T43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="U43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="V43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="W43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="X43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="Y43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
     </row>
     <row r="44">
@@ -8199,19 +8199,19 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L5" t="n">
-        <v>235.7664149699872</v>
+        <v>260.3515428840269</v>
       </c>
       <c r="M5" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N5" t="n">
-        <v>229.4130635965909</v>
+        <v>255.0333547912217</v>
       </c>
       <c r="O5" t="n">
-        <v>230.0982114216867</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P5" t="n">
-        <v>231.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q5" t="n">
         <v>212.3149906599047</v>
@@ -8281,16 +8281,16 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M6" t="n">
-        <v>142.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N6" t="n">
-        <v>131.3417120833333</v>
+        <v>156.9620032779641</v>
       </c>
       <c r="O6" t="n">
-        <v>142.5962444444444</v>
+        <v>168.2165356390753</v>
       </c>
       <c r="P6" t="n">
-        <v>133.9744074143302</v>
+        <v>158.5595353283699</v>
       </c>
       <c r="Q6" t="n">
         <v>139.9817740860215</v>
@@ -8357,16 +8357,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L7" t="n">
-        <v>134.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M7" t="n">
-        <v>138.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N7" t="n">
-        <v>127.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O7" t="n">
-        <v>138.4565384518428</v>
+        <v>163.0416663658825</v>
       </c>
       <c r="P7" t="n">
         <v>135.0065633140411</v>
@@ -8436,19 +8436,19 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L8" t="n">
-        <v>235.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M8" t="n">
-        <v>256.3462332272727</v>
+        <v>255.9665244219036</v>
       </c>
       <c r="N8" t="n">
-        <v>255.4130635965909</v>
+        <v>255.0333547912217</v>
       </c>
       <c r="O8" t="n">
-        <v>255.0477063711817</v>
+        <v>254.6833393357264</v>
       </c>
       <c r="P8" t="n">
-        <v>257.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q8" t="n">
         <v>212.3149906599047</v>
@@ -8512,25 +8512,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K9" t="n">
-        <v>163.841438974359</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L9" t="n">
-        <v>164.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M9" t="n">
-        <v>168.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N9" t="n">
-        <v>156.2912070328283</v>
+        <v>155.926839997373</v>
       </c>
       <c r="O9" t="n">
-        <v>142.5962444444444</v>
+        <v>168.2165356390753</v>
       </c>
       <c r="P9" t="n">
-        <v>133.9744074143302</v>
+        <v>159.5946986089611</v>
       </c>
       <c r="Q9" t="n">
-        <v>139.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8594,13 +8594,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M10" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N10" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O10" t="n">
         <v>163.0416663658825</v>
@@ -8670,22 +8670,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>246.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L11" t="n">
-        <v>261.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M11" t="n">
-        <v>255.2957281767677</v>
+        <v>254.9313611413124</v>
       </c>
       <c r="N11" t="n">
-        <v>229.4130635965909</v>
+        <v>255.0333547912217</v>
       </c>
       <c r="O11" t="n">
-        <v>230.0982114216867</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P11" t="n">
-        <v>257.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q11" t="n">
         <v>212.3149906599047</v>
@@ -8749,22 +8749,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K12" t="n">
-        <v>163.841438974359</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L12" t="n">
-        <v>164.5543797798742</v>
+        <v>163.1395076939139</v>
       </c>
       <c r="M12" t="n">
-        <v>168.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N12" t="n">
-        <v>156.2912070328283</v>
+        <v>156.9620032779641</v>
       </c>
       <c r="O12" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>133.9744074143302</v>
+        <v>159.5946986089611</v>
       </c>
       <c r="Q12" t="n">
         <v>139.9817740860215</v>
@@ -8831,13 +8831,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M13" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N13" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O13" t="n">
         <v>163.0416663658825</v>
@@ -8907,22 +8907,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>246.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L14" t="n">
-        <v>261.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M14" t="n">
-        <v>230.3462332272727</v>
+        <v>255.9665244219036</v>
       </c>
       <c r="N14" t="n">
-        <v>229.4130635965909</v>
+        <v>255.0333547912217</v>
       </c>
       <c r="O14" t="n">
-        <v>255.0477063711817</v>
+        <v>254.6833393357264</v>
       </c>
       <c r="P14" t="n">
-        <v>257.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q14" t="n">
         <v>212.3149906599047</v>
@@ -8989,22 +8989,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L15" t="n">
-        <v>163.5038747293692</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M15" t="n">
-        <v>168.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N15" t="n">
-        <v>157.3417120833333</v>
+        <v>156.9620032779641</v>
       </c>
       <c r="O15" t="n">
-        <v>142.5962444444444</v>
+        <v>168.2165356390753</v>
       </c>
       <c r="P15" t="n">
-        <v>133.9744074143302</v>
+        <v>158.5595353283699</v>
       </c>
       <c r="Q15" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9068,13 +9068,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M16" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N16" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O16" t="n">
         <v>163.0416663658825</v>
@@ -9144,22 +9144,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>220.0898510449805</v>
+        <v>247.6798763052967</v>
       </c>
       <c r="L17" t="n">
-        <v>263.7664149699872</v>
+        <v>263.3564402303034</v>
       </c>
       <c r="M17" t="n">
-        <v>258.3462332272727</v>
+        <v>257.9362584875889</v>
       </c>
       <c r="N17" t="n">
-        <v>256.2817504652778</v>
+        <v>255.8883403615407</v>
       </c>
       <c r="O17" t="n">
         <v>230.0982114216867</v>
       </c>
       <c r="P17" t="n">
-        <v>259.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9226,22 +9226,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L18" t="n">
-        <v>138.5543797798742</v>
+        <v>166.1444050401903</v>
       </c>
       <c r="M18" t="n">
-        <v>142.1340339220183</v>
+        <v>168.6093106869682</v>
       </c>
       <c r="N18" t="n">
-        <v>158.2103989520202</v>
+        <v>158.9317373436494</v>
       </c>
       <c r="O18" t="n">
-        <v>170.5962444444444</v>
+        <v>170.1862697047606</v>
       </c>
       <c r="P18" t="n">
-        <v>161.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q18" t="n">
-        <v>167.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9308,10 +9308,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M19" t="n">
-        <v>166.9257839476051</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N19" t="n">
-        <v>155.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O19" t="n">
         <v>163.0416663658825</v>
@@ -9381,7 +9381,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L20" t="n">
         <v>417.6612145504504</v>
@@ -9460,19 +9460,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L21" t="n">
-        <v>299.7048467786739</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>142.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N21" t="n">
-        <v>372.3417120833333</v>
+        <v>186.8580120236956</v>
       </c>
       <c r="O21" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P21" t="n">
         <v>318.4627686399372</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9697,25 +9697,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L24" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M24" t="n">
-        <v>142.1340339220183</v>
+        <v>312.04082470182</v>
       </c>
       <c r="N24" t="n">
-        <v>357.73449794694</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P24" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q24" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9855,7 +9855,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L26" t="n">
         <v>417.6612145504504</v>
@@ -9934,25 +9934,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L27" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M27" t="n">
-        <v>142.1340339220183</v>
+        <v>197.6503338623806</v>
       </c>
       <c r="N27" t="n">
-        <v>231.1106999087204</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O27" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P27" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q27" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10092,13 +10092,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>324.0888343889188</v>
+        <v>226.4727136557642</v>
       </c>
       <c r="L29" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M29" t="n">
-        <v>449.5135334928325</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N29" t="n">
         <v>437.3469244119842</v>
@@ -10171,19 +10171,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K30" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L30" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M30" t="n">
-        <v>368.526819785625</v>
+        <v>183.0115685892478</v>
       </c>
       <c r="N30" t="n">
-        <v>131.3417120833333</v>
+        <v>346.7357097663615</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P30" t="n">
         <v>318.4627686399372</v>
@@ -10329,13 +10329,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>315.8723521211968</v>
+        <v>226.4727136557642</v>
       </c>
       <c r="L32" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M32" t="n">
-        <v>445.3462332272727</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N32" t="n">
         <v>437.3469244119842</v>
@@ -10344,7 +10344,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P32" t="n">
-        <v>231.2329957552695</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q32" t="n">
         <v>212.3149906599047</v>
@@ -10411,22 +10411,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L33" t="n">
-        <v>353.5543797798742</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M33" t="n">
-        <v>357.1340339220183</v>
+        <v>357.5280316050465</v>
       </c>
       <c r="N33" t="n">
-        <v>346.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>222.2855777193561</v>
+        <v>183.4737791116739</v>
       </c>
       <c r="P33" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q33" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10572,16 +10572,16 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M35" t="n">
-        <v>445.3462332272727</v>
+        <v>348.0675319949004</v>
       </c>
       <c r="N35" t="n">
         <v>437.3469244119842</v>
       </c>
       <c r="O35" t="n">
-        <v>372.5271208127775</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P35" t="n">
-        <v>231.2329957552695</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q35" t="n">
         <v>212.3149906599047</v>
@@ -10648,16 +10648,16 @@
         <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
-        <v>353.5543797798742</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M36" t="n">
-        <v>357.1340339220183</v>
+        <v>348.8252438198737</v>
       </c>
       <c r="N36" t="n">
-        <v>337.6548433964646</v>
+        <v>346.7357097663615</v>
       </c>
       <c r="O36" t="n">
-        <v>357.5962444444444</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P36" t="n">
         <v>133.9744074143302</v>
@@ -10809,16 +10809,16 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M38" t="n">
-        <v>445.3462332272727</v>
+        <v>348.0675319949004</v>
       </c>
       <c r="N38" t="n">
         <v>437.3469244119842</v>
       </c>
       <c r="O38" t="n">
-        <v>372.5271208127775</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P38" t="n">
-        <v>231.2329957552695</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q38" t="n">
         <v>212.3149906599047</v>
@@ -10882,22 +10882,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K39" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L39" t="n">
-        <v>353.5543797798742</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M39" t="n">
-        <v>357.1340339220183</v>
+        <v>357.5280316050465</v>
       </c>
       <c r="N39" t="n">
-        <v>346.3417120833333</v>
+        <v>172.2192467505628</v>
       </c>
       <c r="O39" t="n">
-        <v>278.8138621077482</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q39" t="n">
         <v>210.0772877358491</v>
@@ -11040,13 +11040,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>220.0898510449805</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L41" t="n">
-        <v>417.6612145504504</v>
+        <v>314.1588986527692</v>
       </c>
       <c r="M41" t="n">
-        <v>442.643829968084</v>
+        <v>443.7704968446156</v>
       </c>
       <c r="N41" t="n">
         <v>437.3469244119842</v>
@@ -11122,13 +11122,13 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L42" t="n">
-        <v>351.5543797798742</v>
+        <v>351.9786433972171</v>
       </c>
       <c r="M42" t="n">
-        <v>248.4158140521313</v>
+        <v>355.5582975393612</v>
       </c>
       <c r="N42" t="n">
-        <v>344.3417120833333</v>
+        <v>168.3593638339673</v>
       </c>
       <c r="O42" t="n">
         <v>142.5962444444444</v>
@@ -11137,7 +11137,7 @@
         <v>318.4627686399372</v>
       </c>
       <c r="Q42" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -22750,7 +22750,7 @@
         <v>354.683041620683</v>
       </c>
       <c r="E5" t="n">
-        <v>381.9303700722618</v>
+        <v>356.3100788776309</v>
       </c>
       <c r="F5" t="n">
         <v>406.8760457417114</v>
@@ -22762,10 +22762,10 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I5" t="n">
-        <v>210.4758895704059</v>
+        <v>184.8555983757751</v>
       </c>
       <c r="J5" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -22798,7 +22798,7 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U5" t="n">
-        <v>251.3456529078365</v>
+        <v>240.7285897782182</v>
       </c>
       <c r="V5" t="n">
         <v>327.7522584701349</v>
@@ -22810,7 +22810,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y5" t="n">
-        <v>386.2379386560536</v>
+        <v>360.6176474614227</v>
       </c>
     </row>
     <row r="6">
@@ -22832,16 +22832,16 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F6" t="n">
-        <v>145.0692123933839</v>
+        <v>122.502859909153</v>
       </c>
       <c r="G6" t="n">
-        <v>137.3435171632106</v>
+        <v>111.7232259685798</v>
       </c>
       <c r="H6" t="n">
-        <v>112.2354442364965</v>
+        <v>86.61515304186563</v>
       </c>
       <c r="I6" t="n">
-        <v>89.39663285141508</v>
+        <v>63.77634165678425</v>
       </c>
       <c r="J6" t="n">
         <v>0.7465913262578567</v>
@@ -22941,19 +22941,19 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>86.16204325169439</v>
+        <v>60.54175205706355</v>
       </c>
       <c r="R7" t="n">
-        <v>177.2933913771695</v>
+        <v>151.6731001825387</v>
       </c>
       <c r="S7" t="n">
-        <v>224.0165980369723</v>
+        <v>198.3963068423414</v>
       </c>
       <c r="T7" t="n">
-        <v>227.9455894282815</v>
+        <v>208.1006776791572</v>
       </c>
       <c r="U7" t="n">
         <v>286.3190293564909</v>
@@ -22990,19 +22990,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F8" t="n">
-        <v>395.924535096324</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
-        <v>389.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H8" t="n">
-        <v>313.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I8" t="n">
-        <v>184.4758895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -23023,19 +23023,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>149.8691179411497</v>
+        <v>124.2488267465189</v>
       </c>
       <c r="S8" t="n">
-        <v>209.0200695862453</v>
+        <v>183.3997783916145</v>
       </c>
       <c r="T8" t="n">
-        <v>223.0958495641314</v>
+        <v>197.4755583695005</v>
       </c>
       <c r="U8" t="n">
-        <v>251.3456529078365</v>
+        <v>238.7699996381505</v>
       </c>
       <c r="V8" t="n">
         <v>327.7522584701349</v>
@@ -23063,25 +23063,25 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D9" t="n">
-        <v>121.4450655646388</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E9" t="n">
-        <v>131.6450804554009</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F9" t="n">
-        <v>119.0692123933839</v>
+        <v>123.2494512354109</v>
       </c>
       <c r="G9" t="n">
-        <v>114.4427171632106</v>
+        <v>111.7232259685798</v>
       </c>
       <c r="H9" t="n">
-        <v>112.2354442364965</v>
+        <v>86.61515304186563</v>
       </c>
       <c r="I9" t="n">
-        <v>89.39663285141508</v>
+        <v>63.77634165678425</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -23151,16 +23151,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.7167873157914</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H10" t="n">
-        <v>136.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I10" t="n">
-        <v>129.4504749272583</v>
+        <v>132.254763809386</v>
       </c>
       <c r="J10" t="n">
-        <v>67.35918011667277</v>
+        <v>67.73888892204195</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -23178,10 +23178,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>86.16204325169439</v>
+        <v>60.54175205706355</v>
       </c>
       <c r="R10" t="n">
         <v>177.2933913771695</v>
@@ -23218,13 +23218,13 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C11" t="n">
-        <v>365.2728917710076</v>
+        <v>339.6526005763767</v>
       </c>
       <c r="D11" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E11" t="n">
-        <v>381.9303700722618</v>
+        <v>356.3100788776309</v>
       </c>
       <c r="F11" t="n">
         <v>406.8760457417114</v>
@@ -23233,10 +23233,10 @@
         <v>415.302737515135</v>
       </c>
       <c r="H11" t="n">
-        <v>313.4748021157671</v>
+        <v>316.9084496315363</v>
       </c>
       <c r="I11" t="n">
-        <v>184.4758895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J11" t="n">
         <v>11.94928935461252</v>
@@ -23266,16 +23266,16 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S11" t="n">
-        <v>209.0200695862453</v>
+        <v>183.3997783916145</v>
       </c>
       <c r="T11" t="n">
         <v>223.0958495641314</v>
       </c>
       <c r="U11" t="n">
-        <v>225.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V11" t="n">
-        <v>304.8514584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W11" t="n">
         <v>349.240968717413</v>
@@ -23312,10 +23312,10 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H12" t="n">
-        <v>89.33464423649647</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I12" t="n">
-        <v>63.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J12" t="n">
         <v>0.7465913262578567</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>74.15783415264313</v>
+        <v>74.5375429580123</v>
       </c>
       <c r="S12" t="n">
-        <v>145.6831711038378</v>
+        <v>146.062879909207</v>
       </c>
       <c r="T12" t="n">
-        <v>200.1647286948216</v>
+        <v>174.5444375001908</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9413820809748</v>
+        <v>203.375029596744</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23394,13 +23394,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I13" t="n">
-        <v>155.4504749272583</v>
+        <v>132.254763809386</v>
       </c>
       <c r="J13" t="n">
-        <v>93.35918011667277</v>
+        <v>67.73888892204195</v>
       </c>
       <c r="K13" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23418,16 +23418,16 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>60.16204325169439</v>
+        <v>60.54175205706355</v>
       </c>
       <c r="R13" t="n">
-        <v>151.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S13" t="n">
-        <v>198.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T13" t="n">
-        <v>208.1233462948377</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U13" t="n">
         <v>286.3190293564909</v>
@@ -23458,25 +23458,25 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D14" t="n">
-        <v>343.7315309752955</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E14" t="n">
-        <v>355.9303700722618</v>
+        <v>359.3640175880309</v>
       </c>
       <c r="F14" t="n">
-        <v>406.8760457417114</v>
+        <v>381.2557545470806</v>
       </c>
       <c r="G14" t="n">
-        <v>389.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H14" t="n">
-        <v>313.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I14" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -23518,10 +23518,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X14" t="n">
-        <v>369.731100678469</v>
+        <v>344.1108094838382</v>
       </c>
       <c r="Y14" t="n">
-        <v>386.2379386560536</v>
+        <v>360.6176474614227</v>
       </c>
     </row>
     <row r="15">
@@ -23543,16 +23543,16 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F15" t="n">
-        <v>122.9150037196417</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>111.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H15" t="n">
-        <v>86.23544423649646</v>
+        <v>90.41568307852349</v>
       </c>
       <c r="I15" t="n">
-        <v>63.39663285141508</v>
+        <v>63.77634165678425</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23582,10 +23582,10 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S15" t="n">
-        <v>171.6831711038378</v>
+        <v>146.062879909207</v>
       </c>
       <c r="T15" t="n">
-        <v>200.1647286948216</v>
+        <v>174.5444375001908</v>
       </c>
       <c r="U15" t="n">
         <v>225.9413820809748</v>
@@ -23631,13 +23631,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I16" t="n">
-        <v>155.4504749272583</v>
+        <v>132.254763809386</v>
       </c>
       <c r="J16" t="n">
-        <v>93.35918011667277</v>
+        <v>67.73888892204195</v>
       </c>
       <c r="K16" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -23655,16 +23655,16 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>60.16204325169439</v>
+        <v>60.54175205706355</v>
       </c>
       <c r="R16" t="n">
-        <v>151.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S16" t="n">
-        <v>198.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T16" t="n">
-        <v>208.1233462948377</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U16" t="n">
         <v>286.3190293564909</v>
@@ -23701,16 +23701,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F17" t="n">
-        <v>406.8760457417114</v>
+        <v>392.5654507069698</v>
       </c>
       <c r="G17" t="n">
-        <v>415.302737515135</v>
+        <v>387.7127122548189</v>
       </c>
       <c r="H17" t="n">
-        <v>339.4748021157671</v>
+        <v>311.884776855451</v>
       </c>
       <c r="I17" t="n">
-        <v>210.4758895704059</v>
+        <v>182.8858643100898</v>
       </c>
       <c r="J17" t="n">
         <v>11.94928935461252</v>
@@ -23734,19 +23734,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>121.8691179411497</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S17" t="n">
-        <v>181.0200695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T17" t="n">
-        <v>195.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U17" t="n">
-        <v>226.6832529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,13 +23783,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>137.3435171632106</v>
+        <v>109.7534919028945</v>
       </c>
       <c r="H18" t="n">
-        <v>112.2354442364965</v>
+        <v>84.64541897618032</v>
       </c>
       <c r="I18" t="n">
-        <v>89.39663285141508</v>
+        <v>65.09533860212863</v>
       </c>
       <c r="J18" t="n">
         <v>0.7465913262578567</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>72.15783415264313</v>
+        <v>72.56780889232699</v>
       </c>
       <c r="S18" t="n">
-        <v>143.6831711038378</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T18" t="n">
-        <v>172.1647286948216</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U18" t="n">
-        <v>201.2789820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23847,7 +23847,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>179.8319801819373</v>
+        <v>152.2419549216212</v>
       </c>
       <c r="C19" t="n">
         <v>167.2468210986278</v>
@@ -23856,13 +23856,13 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E19" t="n">
-        <v>146.4339626465692</v>
+        <v>118.843937386253</v>
       </c>
       <c r="F19" t="n">
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.9909793584588</v>
+        <v>145.5422199979494</v>
       </c>
       <c r="H19" t="n">
         <v>162.2271725074396</v>
@@ -23898,22 +23898,22 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S19" t="n">
-        <v>224.0165980369723</v>
+        <v>196.4265727766561</v>
       </c>
       <c r="T19" t="n">
-        <v>199.9455894282815</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U19" t="n">
-        <v>258.3190293564909</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
       </c>
       <c r="W19" t="n">
-        <v>258.522998336591</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X19" t="n">
-        <v>203.687187762851</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y19" t="n">
         <v>218.5846533520948</v>
@@ -23926,28 +23926,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C20" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D20" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E20" t="n">
-        <v>380.1334596426677</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F20" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H20" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J20" t="n">
         <v>11.94928935461252</v>
@@ -23971,7 +23971,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>149.8691179411497</v>
@@ -23992,10 +23992,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X20" t="n">
-        <v>369.731100678469</v>
+        <v>167.4364142495718</v>
       </c>
       <c r="Y20" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="21">
@@ -24005,7 +24005,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
         <v>172.7084989883157</v>
@@ -24023,13 +24023,13 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
-        <v>112.2354442364965</v>
+        <v>76.13065030334459</v>
       </c>
       <c r="I21" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -24053,16 +24053,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>114.7217985819518</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24084,7 +24084,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>46.64501259656927</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C22" t="n">
         <v>167.2468210986278</v>
@@ -24153,7 +24153,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y22" t="n">
-        <v>218.5846533520948</v>
+        <v>85.39768576672677</v>
       </c>
     </row>
     <row r="23">
@@ -24163,31 +24163,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C23" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D23" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E23" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F23" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H23" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I23" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -24208,7 +24208,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>149.8691179411497</v>
@@ -24217,7 +24217,7 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T23" t="n">
-        <v>22.77233891874386</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U23" t="n">
         <v>251.3456529078365</v>
@@ -24232,7 +24232,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y23" t="n">
-        <v>386.2379386560536</v>
+        <v>183.9432522271564</v>
       </c>
     </row>
     <row r="24">
@@ -24242,13 +24242,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>31.81847845125367</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E24" t="n">
         <v>157.6450804554009</v>
@@ -24290,28 +24290,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9413820809748</v>
+        <v>134.8347431830299</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -24330,7 +24330,7 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E25" t="n">
-        <v>13.24699506120115</v>
+        <v>146.4339626465692</v>
       </c>
       <c r="F25" t="n">
         <v>145.4210480229312</v>
@@ -24363,13 +24363,13 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>177.2933913771695</v>
+        <v>132.9899077786024</v>
       </c>
       <c r="S25" t="n">
         <v>224.0165980369723</v>
@@ -24421,10 +24421,10 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -24448,28 +24448,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S26" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>223.0958495641314</v>
+        <v>219.8305335069347</v>
       </c>
       <c r="U26" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V26" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W26" t="n">
-        <v>108.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X26" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y26" t="n">
-        <v>305.2594355222217</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="27">
@@ -24479,22 +24479,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E27" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>137.3435171632106</v>
+        <v>110.3577089611572</v>
       </c>
       <c r="H27" t="n">
         <v>112.2354442364965</v>
@@ -24527,10 +24527,10 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S27" t="n">
-        <v>136.4689518019017</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
         <v>200.1647286948216</v>
@@ -24542,7 +24542,7 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -24579,13 +24579,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I28" t="n">
-        <v>137.8921792844459</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -24618,7 +24618,7 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V28" t="n">
-        <v>252.137643323828</v>
+        <v>118.95067573846</v>
       </c>
       <c r="W28" t="n">
         <v>286.522998336591</v>
@@ -24637,10 +24637,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>382.7338416634806</v>
+        <v>167.3398439804523</v>
       </c>
       <c r="C29" t="n">
-        <v>124.2728917710076</v>
+        <v>149.8788940879793</v>
       </c>
       <c r="D29" t="n">
         <v>354.683041620683</v>
@@ -24649,10 +24649,10 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F29" t="n">
-        <v>406.8760457417114</v>
+        <v>191.4820480586832</v>
       </c>
       <c r="G29" t="n">
-        <v>415.302737515135</v>
+        <v>385.4435215116183</v>
       </c>
       <c r="H29" t="n">
         <v>339.4748021157671</v>
@@ -24685,7 +24685,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>209.0200695862453</v>
@@ -24697,13 +24697,13 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V29" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W29" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X29" t="n">
-        <v>167.4489998930138</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y29" t="n">
         <v>386.2379386560536</v>
@@ -24722,10 +24722,10 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F30" t="n">
         <v>145.0692123933839</v>
@@ -24740,7 +24740,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -24770,22 +24770,22 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T30" t="n">
-        <v>200.1647286948216</v>
+        <v>10.44569553561035</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9413820809748</v>
+        <v>10.54738439794659</v>
       </c>
       <c r="V30" t="n">
-        <v>232.8005871494253</v>
+        <v>17.40658946639704</v>
       </c>
       <c r="W30" t="n">
-        <v>10.69498316091961</v>
+        <v>36.30098547789137</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
-        <v>23.01961832707943</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="31">
@@ -24795,7 +24795,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>46.64501259656927</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C31" t="n">
         <v>167.2468210986278</v>
@@ -24864,7 +24864,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y31" t="n">
-        <v>218.5846533520948</v>
+        <v>85.39768576672677</v>
       </c>
     </row>
     <row r="32">
@@ -24877,19 +24877,19 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C32" t="n">
-        <v>365.2728917710076</v>
+        <v>149.8788940879793</v>
       </c>
       <c r="D32" t="n">
-        <v>139.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E32" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F32" t="n">
-        <v>191.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>200.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H32" t="n">
         <v>339.4748021157671</v>
@@ -24925,13 +24925,13 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S32" t="n">
-        <v>19.64806958624538</v>
+        <v>19.30103642703409</v>
       </c>
       <c r="T32" t="n">
-        <v>223.0958495641314</v>
+        <v>7.701851881103124</v>
       </c>
       <c r="U32" t="n">
-        <v>251.3456529078365</v>
+        <v>35.95165522480826</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24953,22 +24953,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>54.16154731977191</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>112.2354442364965</v>
@@ -25001,10 +25001,10 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
         <v>200.1647286948216</v>
@@ -25022,7 +25022,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
-        <v>205.6826957773044</v>
+        <v>138.8811473284249</v>
       </c>
     </row>
     <row r="34">
@@ -25053,13 +25053,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I34" t="n">
-        <v>155.4504749272583</v>
+        <v>137.8921792844459</v>
       </c>
       <c r="J34" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -25092,7 +25092,7 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V34" t="n">
-        <v>118.9506757384599</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W34" t="n">
         <v>286.522998336591</v>
@@ -25111,13 +25111,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>382.7338416634806</v>
+        <v>203.0055077188142</v>
       </c>
       <c r="C35" t="n">
-        <v>150.2728917710076</v>
+        <v>149.8788940879793</v>
       </c>
       <c r="D35" t="n">
-        <v>139.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E35" t="n">
         <v>381.9303700722618</v>
@@ -25156,7 +25156,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>149.8691179411497</v>
@@ -25165,22 +25165,22 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T35" t="n">
-        <v>223.0958495641314</v>
+        <v>7.701851881103124</v>
       </c>
       <c r="U35" t="n">
-        <v>36.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W35" t="n">
-        <v>349.240968717413</v>
+        <v>133.8469710343848</v>
       </c>
       <c r="X35" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y35" t="n">
-        <v>196.8659386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="36">
@@ -25190,22 +25190,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C36" t="n">
-        <v>106.4106488632542</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>5.577355383807486</v>
       </c>
       <c r="E36" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H36" t="n">
         <v>112.2354442364965</v>
@@ -25238,10 +25238,10 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
         <v>200.1647286948216</v>
@@ -25253,10 +25253,10 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W36" t="n">
-        <v>251.6949831609196</v>
+        <v>36.30098547789137</v>
       </c>
       <c r="X36" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>205.6826957773044</v>
@@ -25272,7 +25272,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C37" t="n">
-        <v>167.2468210986278</v>
+        <v>34.05985351325981</v>
       </c>
       <c r="D37" t="n">
         <v>148.6154730182124</v>
@@ -25317,7 +25317,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R37" t="n">
-        <v>44.10642379180143</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S37" t="n">
         <v>224.0165980369723</v>
@@ -25348,25 +25348,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>382.7338416634806</v>
+        <v>193.0148085042693</v>
       </c>
       <c r="C38" t="n">
-        <v>365.2728917710076</v>
+        <v>149.8788940879793</v>
       </c>
       <c r="D38" t="n">
-        <v>354.683041620683</v>
+        <v>139.2890439376547</v>
       </c>
       <c r="E38" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F38" t="n">
-        <v>191.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>200.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H38" t="n">
-        <v>339.4748021157671</v>
+        <v>124.0808044327389</v>
       </c>
       <c r="I38" t="n">
         <v>210.4758895704059</v>
@@ -25393,13 +25393,13 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
-        <v>29.63876880079016</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T38" t="n">
         <v>223.0958495641314</v>
@@ -25408,7 +25408,7 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V38" t="n">
-        <v>112.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W38" t="n">
         <v>349.240968717413</v>
@@ -25430,10 +25430,10 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C39" t="n">
-        <v>167.4533332754039</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>28.97478758692554</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -25442,7 +25442,7 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H39" t="n">
         <v>112.2354442364965</v>
@@ -25490,7 +25490,7 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
-        <v>36.69498316091961</v>
+        <v>36.30098547789137</v>
       </c>
       <c r="X39" t="n">
         <v>205.7729852034775</v>
@@ -25563,7 +25563,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U40" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25575,7 +25575,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y40" t="n">
-        <v>85.39768576672674</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="41">
@@ -25585,7 +25585,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>169.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C41" t="n">
         <v>365.2728917710076</v>
@@ -25594,22 +25594,22 @@
         <v>354.683041620683</v>
       </c>
       <c r="E41" t="n">
-        <v>168.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F41" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>415.302737515135</v>
+        <v>201.8784738977921</v>
       </c>
       <c r="H41" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I41" t="n">
-        <v>210.4758895704059</v>
+        <v>44.43178674540761</v>
       </c>
       <c r="J41" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -25651,10 +25651,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X41" t="n">
-        <v>156.731100678469</v>
+        <v>156.3068370611261</v>
       </c>
       <c r="Y41" t="n">
-        <v>208.6182378705984</v>
+        <v>172.8136750387107</v>
       </c>
     </row>
     <row r="42">
@@ -25685,10 +25685,10 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -25718,16 +25718,16 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9413820809748</v>
+        <v>30.30601227295384</v>
       </c>
       <c r="V42" t="n">
-        <v>19.80058714942527</v>
+        <v>19.37632353208235</v>
       </c>
       <c r="W42" t="n">
-        <v>134.1655212368917</v>
+        <v>38.27071954357669</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -25791,7 +25791,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R43" t="n">
-        <v>44.10642379180143</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S43" t="n">
         <v>224.0165980369723</v>
@@ -25806,7 +25806,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W43" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X43" t="n">
         <v>225.7096553890372</v>
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>327897.5868709115</v>
+        <v>350064.5328762545</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>350379.9730845937</v>
+        <v>350064.5328762545</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>350379.9730845935</v>
+        <v>350064.5328762547</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>350379.9730845935</v>
+        <v>350064.5328762547</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>352026.7318511437</v>
+        <v>351700.8745024338</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>507017.9003687725</v>
+        <v>507028.2310008515</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>507017.9003687725</v>
+        <v>507028.2310008513</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>507017.9003687725</v>
+        <v>507028.2310008513</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>507017.9003687726</v>
+        <v>488505.1665306334</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>488220.3124503887</v>
+        <v>488505.1665306334</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>488220.3124503888</v>
+        <v>488505.1665306334</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>488220.3124503887</v>
+        <v>488505.1665306334</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>486774.3441489747</v>
+        <v>487081.0800200351</v>
       </c>
     </row>
     <row r="16">
@@ -26261,46 +26261,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69879.81359544017</v>
+        <v>69879.81359544014</v>
       </c>
       <c r="C2" t="n">
-        <v>69879.81359544015</v>
+        <v>74597.63547237263</v>
       </c>
       <c r="D2" t="n">
-        <v>74664.77104961485</v>
+        <v>74597.63547237263</v>
       </c>
       <c r="E2" t="n">
-        <v>74664.77104961485</v>
+        <v>74597.63547237263</v>
       </c>
       <c r="F2" t="n">
-        <v>74664.77104961485</v>
+        <v>74597.63547237263</v>
       </c>
       <c r="G2" t="n">
-        <v>75015.25300292439</v>
+        <v>74945.90033124233</v>
       </c>
       <c r="H2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="I2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="J2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="K2" t="n">
-        <v>108002.238462606</v>
+        <v>104062.1476317649</v>
       </c>
       <c r="L2" t="n">
-        <v>104001.521742606</v>
+        <v>104062.1476317649</v>
       </c>
       <c r="M2" t="n">
-        <v>104001.521742606</v>
+        <v>104062.147631765</v>
       </c>
       <c r="N2" t="n">
-        <v>104001.521742606</v>
+        <v>104062.147631765</v>
       </c>
       <c r="O2" t="n">
-        <v>103693.774302606</v>
+        <v>103759.0573236672</v>
       </c>
       <c r="P2" t="n">
         <v>69879.81359544017</v>
@@ -26316,10 +26316,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>8277.165051769143</v>
       </c>
       <c r="D3" t="n">
-        <v>8076.38</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26328,10 +26328,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>548.1700000000001</v>
+        <v>539.8745613933579</v>
       </c>
       <c r="H3" t="n">
-        <v>57469.317</v>
+        <v>57583.78714233168</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21501.48110628928</v>
+        <v>20948.32715815079</v>
       </c>
       <c r="C4" t="n">
-        <v>21501.48110628928</v>
+        <v>22413.55190523866</v>
       </c>
       <c r="D4" t="n">
-        <v>23026.20207384747</v>
+        <v>22413.55190523866</v>
       </c>
       <c r="E4" t="n">
-        <v>23026.20207384747</v>
+        <v>22413.55190523866</v>
       </c>
       <c r="F4" t="n">
-        <v>23026.20207384747</v>
+        <v>22413.55190523866</v>
       </c>
       <c r="G4" t="n">
-        <v>23137.88272891696</v>
+        <v>22521.71332020263</v>
       </c>
       <c r="H4" t="n">
-        <v>33649.14617662696</v>
+        <v>32788.77882333349</v>
       </c>
       <c r="I4" t="n">
-        <v>33649.14617662696</v>
+        <v>32788.77882333349</v>
       </c>
       <c r="J4" t="n">
-        <v>33649.14617662696</v>
+        <v>32788.77882333349</v>
       </c>
       <c r="K4" t="n">
-        <v>33649.14617662696</v>
+        <v>31564.41293878062</v>
       </c>
       <c r="L4" t="n">
-        <v>32374.32258066736</v>
+        <v>31564.41293878062</v>
       </c>
       <c r="M4" t="n">
-        <v>32374.32258066736</v>
+        <v>31564.41293878061</v>
       </c>
       <c r="N4" t="n">
-        <v>32374.32258066736</v>
+        <v>31564.41293878061</v>
       </c>
       <c r="O4" t="n">
-        <v>32276.259227132</v>
+        <v>31470.28148752794</v>
       </c>
       <c r="P4" t="n">
-        <v>21501.48110628928</v>
+        <v>20948.32715815079</v>
       </c>
     </row>
     <row r="5">
@@ -26420,43 +26420,43 @@
         <v>33627.6</v>
       </c>
       <c r="C5" t="n">
-        <v>33627.6</v>
+        <v>35185.31370463355</v>
       </c>
       <c r="D5" t="n">
-        <v>35208.4</v>
+        <v>35185.31370463355</v>
       </c>
       <c r="E5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="F5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="G5" t="n">
-        <v>1702.4</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="L5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="M5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="N5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="O5" t="n">
-        <v>12950.4</v>
+        <v>12976.19522793445</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14750.73248915088</v>
+        <v>15303.88643728934</v>
       </c>
       <c r="C6" t="n">
-        <v>14750.73248915087</v>
+        <v>8721.604810731267</v>
       </c>
       <c r="D6" t="n">
-        <v>8353.788975767369</v>
+        <v>16998.76986250042</v>
       </c>
       <c r="E6" t="n">
-        <v>50057.76897576737</v>
+        <v>50626.36986250042</v>
       </c>
       <c r="F6" t="n">
-        <v>50057.76897576737</v>
+        <v>50626.36986250042</v>
       </c>
       <c r="G6" t="n">
-        <v>49626.80027400744</v>
+        <v>50206.83891381912</v>
       </c>
       <c r="H6" t="n">
-        <v>2230.975285979064</v>
+        <v>2978.202415939202</v>
       </c>
       <c r="I6" t="n">
-        <v>59700.29228597904</v>
+        <v>60561.98955827089</v>
       </c>
       <c r="J6" t="n">
-        <v>59700.29228597906</v>
+        <v>60561.98955827089</v>
       </c>
       <c r="K6" t="n">
-        <v>59700.29228597904</v>
+        <v>59401.77963385619</v>
       </c>
       <c r="L6" t="n">
-        <v>58555.19916193867</v>
+        <v>59401.7796338562</v>
       </c>
       <c r="M6" t="n">
-        <v>58555.19916193867</v>
+        <v>59401.77963385622</v>
       </c>
       <c r="N6" t="n">
-        <v>58555.19916193867</v>
+        <v>59401.77963385623</v>
       </c>
       <c r="O6" t="n">
-        <v>58467.11507547403</v>
+        <v>59312.58060820486</v>
       </c>
       <c r="P6" t="n">
-        <v>48378.33248915088</v>
+        <v>48931.48643728937</v>
       </c>
     </row>
   </sheetData>
@@ -26730,43 +26730,43 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="L4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26904,37 +26904,37 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,25 +26944,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="H4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -26971,22 +26971,22 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27188,10 +27188,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27200,10 +27200,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="P4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
     </row>
   </sheetData>
@@ -34854,19 +34854,19 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -34936,16 +34936,16 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35012,16 +35012,16 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -35091,19 +35091,19 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M8" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N8" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O8" t="n">
-        <v>24.94949494949495</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35167,25 +35167,25 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>24.94949494949495</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -35249,16 +35249,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O10" t="n">
-        <v>24.58512791403967</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -35325,22 +35325,22 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M11" t="n">
-        <v>24.94949494949495</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35404,22 +35404,22 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="M12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N12" t="n">
-        <v>24.94949494949495</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -35486,13 +35486,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O13" t="n">
         <v>24.58512791403967</v>
@@ -35562,22 +35562,22 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O14" t="n">
-        <v>24.94949494949495</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35644,22 +35644,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35723,13 +35723,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O16" t="n">
         <v>24.58512791403967</v>
@@ -35799,22 +35799,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N17" t="n">
-        <v>26.86868686868687</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35881,22 +35881,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="N18" t="n">
-        <v>26.86868686868687</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -35963,10 +35963,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O19" t="n">
         <v>24.58512791403967</v>
@@ -36036,7 +36036,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L20" t="n">
         <v>181.8947995804632</v>
@@ -36115,19 +36115,19 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>161.1504669987997</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N21" t="n">
-        <v>241</v>
+        <v>55.51629994036225</v>
       </c>
       <c r="O21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P21" t="n">
         <v>184.4883612256069</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36352,25 +36352,25 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L24" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>169.9067907798017</v>
       </c>
       <c r="N24" t="n">
-        <v>226.3927858636066</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P24" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q24" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36510,7 +36510,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L26" t="n">
         <v>181.8947995804632</v>
@@ -36589,25 +36589,25 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>55.51629994036225</v>
       </c>
       <c r="N27" t="n">
-        <v>99.76898782538704</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P27" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q27" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36747,13 +36747,13 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>103.9989833439383</v>
+        <v>6.382862610783645</v>
       </c>
       <c r="L29" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M29" t="n">
-        <v>219.1673002655598</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N29" t="n">
         <v>207.9338608153932</v>
@@ -36826,19 +36826,19 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L30" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>226.3927858636066</v>
+        <v>40.87753466722953</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P30" t="n">
         <v>184.4883612256069</v>
@@ -36984,13 +36984,13 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>95.78250107621625</v>
+        <v>6.382862610783645</v>
       </c>
       <c r="L32" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M32" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N32" t="n">
         <v>207.9338608153932</v>
@@ -36999,7 +36999,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37066,22 +37066,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L33" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M33" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>79.6893332749117</v>
+        <v>40.87753466722948</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37227,16 +37227,16 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M35" t="n">
-        <v>215</v>
+        <v>117.7212987676277</v>
       </c>
       <c r="N35" t="n">
         <v>207.9338608153932</v>
       </c>
       <c r="O35" t="n">
-        <v>142.4289093910907</v>
+        <v>150.7019698410586</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37303,16 +37303,16 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M36" t="n">
-        <v>215</v>
+        <v>206.6912098978554</v>
       </c>
       <c r="N36" t="n">
-        <v>206.3131313131313</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -37464,16 +37464,16 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M38" t="n">
-        <v>215</v>
+        <v>117.7212987676277</v>
       </c>
       <c r="N38" t="n">
         <v>207.9338608153932</v>
       </c>
       <c r="O38" t="n">
-        <v>142.4289093910907</v>
+        <v>150.7019698410586</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -37537,22 +37537,22 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N39" t="n">
-        <v>215</v>
+        <v>40.87753466722948</v>
       </c>
       <c r="O39" t="n">
-        <v>136.2176176633037</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q39" t="n">
         <v>70.09551364982758</v>
@@ -37695,13 +37695,13 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L41" t="n">
-        <v>181.8947995804632</v>
+        <v>78.39248368278189</v>
       </c>
       <c r="M41" t="n">
-        <v>212.2975967408112</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N41" t="n">
         <v>207.9338608153932</v>
@@ -37777,13 +37777,13 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="M42" t="n">
-        <v>106.2817801301129</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N42" t="n">
-        <v>213</v>
+        <v>37.01765175063403</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -37792,7 +37792,7 @@
         <v>184.4883612256069</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
